--- a/www/download/COUNTRY.FIN.EXI382.xlsx
+++ b/www/download/COUNTRY.FIN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Finlândia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934941104294479</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934941104294479</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.934068711656442</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2.378</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2.116</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2.197</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.269</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.413</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.451</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.489</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.488</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.478</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.461</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.481</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.523</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.571</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.353</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.447</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.435</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.463</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.471</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.388</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2.404</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2.406</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2.422</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2.423</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2.558</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2.447</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2.473</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.009</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.772</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.868</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.092</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.179</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.172</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.163</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.178</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.211</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.258</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.034</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.114</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.108</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.133</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.135</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.062</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2.077</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2.083</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2.086</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2.196</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2.109</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4546.835</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4044.12</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4173.152</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4565.122</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4501.088</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4758.344</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4747.796</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4762.79</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>4822.461</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>4701.229</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>4740.226</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>4833.121</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>4904.024</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>4975.564</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4572.334</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>4645.949</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>4654.643</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>4702.879</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>4685.242</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>4515.742</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>4536.368</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4532.435</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>4573.943</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4587.027</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>4849.614</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>4659.659</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>4713.53</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3734.219</t>
+          <t>29452806769.1077</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2586.159</t>
+          <t>12059740672.5266</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2492.024</t>
+          <t>12328850911.1419</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2848.493</t>
+          <t>13378137200.5324</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2884.092</t>
+          <t>14675952481.7169</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3111.362</t>
+          <t>16011092652.6449</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3158.356</t>
+          <t>15077298023.7801</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3233.126</t>
+          <t>14408703447.7136</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3274.489</t>
+          <t>14175816970.3644</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3213.937</t>
+          <t>15384303410.6285</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3304.032</t>
+          <t>15183817964.4522</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3421.877</t>
+          <t>15474601853.8489</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4182.388</t>
+          <t>15042968048.6461</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4261.447</t>
+          <t>16613580459.0235</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3853.173</t>
+          <t>13031695887.0553</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3172.753</t>
+          <t>12847737807.4774</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3934.829</t>
+          <t>13995546978.0615</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3972.848</t>
+          <t>12799624816.5487</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3212.122</t>
+          <t>13068773029.3715</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3801.748</t>
+          <t>11747641619.4506</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3815.19</t>
+          <t>11083969265.438</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3814.434</t>
+          <t>10846648602.4578</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3836.942</t>
+          <t>10665117625.5643</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3841.651</t>
+          <t>10950735042.4107</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4051.951</t>
+          <t>11322185109.1317</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3867.751</t>
+          <t>11419097453.4505</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>3904.434</t>
+          <t>11497958605.9846</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3784442134.59048</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2830719027.56965</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2767993353.87707</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2896261755.69812</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2755617117.55259</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2953964996.08203</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2981660609.90676</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2788710871.47825</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2784054043.87952</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2770922487.57105</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2971661948.23125</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2935289334.67482</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2622300532.84859</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3371829334.32091</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2821327445.18116</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2664603017.98346</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2666931028.99842</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2689741236.69784</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2701586084.34522</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2470064952.72271</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2250635294.14369</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2313468251.97418</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2109522302.8207</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2929386694.73906</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2384442662.41401</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2741908729.78966</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3016513955.78253</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>32462211.1440931</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10129476.0635436</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>9335401.4621034</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9985601.01777037</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>9795000.18581242</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8521348.2677793</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8418635.61447228</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8220244.20701922</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7093103.57223926</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7703969.3716791</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7357469.82874275</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6017597.5610881</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6009333.50224019</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6482604.62912758</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5794622.41891125</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4954990.1015523</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5204115.52795763</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4794182.98592432</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5481729.45142686</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>240202964809.961</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>237122152572.642</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>239405795219.985</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>247857679557.374</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>254358562291.006</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>253813402613.331</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>256248578786.911</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>256222099916.446</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9932.94269094974</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>19505.2999392134</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>21779.8692799181</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>24468.6553930793</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>25821.7817454538</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>31410.066170604</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>31670.5681747551</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30448.9801582758</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>28075.2647979486</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>26652.0782785013</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>28550.2583410482</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>31091.9404206806</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>32493.292924375</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>32787.227844081</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>29266.1327896926</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>35873.474418865</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>37197.7204583633</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>41326.6946764539</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>40047.2269168199</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>39990.1403619054</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>46314.0875870164</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>41728.4571553608</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>45130.6558055809</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>44555.7268015145</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>50309.3553911439</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>45563.9575316593</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>45129.5357618171</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>109788.36031319</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>91642.8428530539</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>102041.263575982</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>113833.780408583</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>131721.000676593</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>171780.026513143</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>162423.984630916</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>150464.855561742</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>135985.515507309</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>144218.94909325</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>152593.905240096</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>166356.765529642</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>167547.256590668</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>185931.044012587</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>146152.412427171</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>166164.414857585</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>188440.39389851</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>190219.69294796</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>189719.106875074</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>176522.868756647</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>188140.925194628</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>167813.248870675</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>174450.295782906</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>174209.272311196</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>191909.574052968</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>184126.746087259</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>182020.275238616</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.0132709412842168</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.0863950202007814</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.0997001504690973</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.0164932453376759</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.046622907670802</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.0532833002846949</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0592607319238276</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.159362210355407</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.176158561720178</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.159879792529268</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.111846521427721</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.165771619028434</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.594930843207494</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.263838284050561</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.365730520426024</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.190703822891348</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.475414608482178</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.477037250199488</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.188976364149489</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.539128769921039</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.695161291846628</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.648794737092306</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.818867840674003</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.31141819474453</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.699328355746902</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.4106053656789</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.294352896689323</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1883.49362016733</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1597.74173255599</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1559.60860597117</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1550.6273453786</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1411.32758901542</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1412.09665666713</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1400.10359217969</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1279.75350900772</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1277.26478133685</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1275.45338898566</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1373.67075682136</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1348.00887929942</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1186.23927116976</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1493.47979550885</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1387.35613944727</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1260.75373455531</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1265.32762205214</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1261.19062066738</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1265.32063338717</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1198.16871066406</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1083.54193434228</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1110.76069678351</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1009.35447000471</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1404.21424841521</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1085.62075070391</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1312.05001812718</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1430.38600077935</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>6713187856.99327</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>3600994885.80856</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>3483112745.52546</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>3821845153.63247</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>4097915489.75861</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>4017824600.89865</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>4358649240.78921</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>4342534226.41306</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>3900948835.55329</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>4202530769.74427</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>3733765758.8601</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>3583915954.29018</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>3165934973.2251</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>3629599380.0125</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>2778953257.38251</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>2375225680.30309</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1976842533.74328</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1873668810.65975</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1948823617.9526</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1390769368.41261</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>1374392406.96852</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1459415243.05593</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>1191229834.47779</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>1204412835.61086</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>1440293300.11031</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1671459392.71027</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1607094591.63223</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7977743818.50495</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3931950338.39811</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3858240248.26638</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4201754566.73459</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4423742009.51747</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4523225321.87277</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4482898775.1343</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>4341323528.86234</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>4073480788.75013</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4515763543.67369</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>4267119297.77945</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>3878989762.94663</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>3028857193.90384</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3611867409.69767</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3073834209.56388</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>3070508047.81103</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2230581694.88464</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2198092876.78238</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2260515519.23186</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1693549489.43294</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1695137998.68734</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1830938401.3335</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1803980304.62593</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1906618256.67052</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2079109648.43597</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2371632858.0486</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3146873832.11458</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-1264555961.51167</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-330955452.589547</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-375127502.740916</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-379909413.102113</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-325826519.758868</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-505400720.974112</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-124249534.345098</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1210697.55071531</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-172531953.196843</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-313232773.929419</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-533353538.919351</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-295073808.656455</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>137077779.321254</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>17731970.3148323</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-294880952.181371</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-695282367.507941</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-253739161.141353</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-324424066.122625</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-311691901.279261</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-302780121.020332</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-320745591.718821</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-371523158.277568</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-612750470.148134</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-702205421.059651</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-638816348.32566</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-700173465.338331</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-1539779240.48236</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1858.49788692489</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>1459.70480329618</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>1404.11539328294</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>1525.05246814396</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1477.12778489134</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>1487.33782685534</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>1483.07475582144</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1483.69785691328</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1502.26590815299</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>1479.37261219743</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>1527.31105255881</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>1571.47049368559</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>1891.96960101263</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>1887.51694202009</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>1894.75462234356</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>1501.18429145955</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1866.88285809174</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>1862.82552632793</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>1504.43632616801</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1844.13593380225</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>1836.77834518965</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>1831.41639102563</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>1835.88238533212</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>1841.51211469123</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>1844.82612525839</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1850.78479560929</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1851.42426349261</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1911.91571941079</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1934.70793665965</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1971.81629181617</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>2077.69979974424</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>1983.46979244677</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1972.20707091631</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1937.08527131665</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1913.68932819031</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1938.05449503721</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1896.9571883949</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1926.37298329776</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>1948.44628099177</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>1943.49621527307</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1935.56523768721</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>1943.35855151215</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1898.47540045714</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1911.55770020535</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1909.79857868004</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1895.8612875817</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1890.78999874961</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>1886.76343034</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1883.92471100855</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>1888.40944502221</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>1893.46420770322</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>1895.76232398675</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1904.61067890788</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1905.79524456178</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>42808.3806294078</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>41588.0900494218</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>47564.6435923097</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50271.9708759964</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>54088.3743299367</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>65837.4306412403</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>67029.7812480872</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>67197.1492716118</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>63709.7986728691</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>67211.5446515541</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>72350.7824958308</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>80822.5960505492</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>87535.8410376593</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>90543.1604343524</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>70563.8180514551</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>78552.8237525945</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>82821.23674097</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>85810.0053483897</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>85160.5848846057</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>82269.893092542</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>83306.7910714752</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>84013.1727307857</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>94106.9215161228</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>100087.072567449</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>109016.723280343</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>111800.932120818</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>113020.580056521</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7765332800.51788</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2769127130.97218</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2895945642.93177</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3092619164.84383</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3399485051.8384</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3918132686.47565</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3625483058.43417</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3374920118.86779</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3232511673.50181</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3617335244.33464</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3370276064.91579</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3701389729.66187</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3428379814.17498</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3791018115.86042</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2673714893.79655</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2864128393.26423</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3013520549.49145</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2766169768.55104</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2916573666.34765</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2548409032.15836</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2171093779.51364</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2077032767.56447</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2252281054.35009</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2471288271.34846</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2581651927.47347</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2686964925.6667</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2685236221.6046</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>32862.4571330747</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>32247.9159607188</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>36877.1243768668</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>37967.1776311484</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>39268.6042183813</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>49601.8631748806</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>49519.1281346912</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>49832.7282112625</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>50604.4493853957</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>54169.7668894189</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>63771.2569160038</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>71342.0966123704</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>75779.2864782349</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>81366.9136577258</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>65722.0340324136</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>75189.2827442551</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>84840.4654300589</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>89898.8154082984</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>87990.0896251127</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>85384.5485157533</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>84878.3933479079</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>87645.6475618561</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>93971.1267762077</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>103362.607595451</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>108021.474492756</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>110909.362145363</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>112111.178673565</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4546.835</t>
+          <t>8843894018.80569</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4044.12</t>
+          <t>4472777276.79139</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4173.152</t>
+          <t>4378486064.13027</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4565.122</t>
+          <t>4596261936.72107</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4501.088</t>
+          <t>4778804221.09824</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4758.344</t>
+          <t>5417161960.29992</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4747.796</t>
+          <t>5160031876.10242</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4762.79</t>
+          <t>4811804112.56824</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4822.461</t>
+          <t>4907154476.70716</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4701.229</t>
+          <t>5428136455.4506</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4740.226</t>
+          <t>5669111157.38958</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4833.121</t>
+          <t>5874686059.54453</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4904.024</t>
+          <t>5134357579.24139</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4975.564</t>
+          <t>6163110607.23745</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4572.334</t>
+          <t>4739999134.57661</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>4645.949</t>
+          <t>4824622685.04626</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>4654.643</t>
+          <t>5223211964.65454</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4702.879</t>
+          <t>5085646575.59603</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>4685.242</t>
+          <t>5189527116.33062</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>4515.742</t>
+          <t>4270285248.22593</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>4536.368</t>
+          <t>3697404937.28818</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>4532.435</t>
+          <t>3921695692.84025</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>4573.943</t>
+          <t>3430430765.09003</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4587.027</t>
+          <t>4001255570.89251</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>4849.614</t>
+          <t>3931111452.31896</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>4659.659</t>
+          <t>4271905185.35614</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>4713.53</t>
+          <t>4203723222.20553</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3734.219</t>
+          <t>9945.92349633309</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2586.159</t>
+          <t>9340.17408870292</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2492.024</t>
+          <t>10687.5192154429</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2848.493</t>
+          <t>12304.793244848</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2884.092</t>
+          <t>14819.7701115554</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3111.362</t>
+          <t>16235.5674663596</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3158.356</t>
+          <t>17510.653113396</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3233.126</t>
+          <t>17364.4210603493</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3274.489</t>
+          <t>13105.3492874734</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3213.937</t>
+          <t>13041.7777621352</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3304.032</t>
+          <t>8579.5255798271</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3421.877</t>
+          <t>9480.49943817876</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4182.388</t>
+          <t>11756.5545594243</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4261.447</t>
+          <t>9176.24677662659</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3853.173</t>
+          <t>4841.78401904151</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3172.753</t>
+          <t>3363.54100833943</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3934.829</t>
+          <t>-2019.22868908892</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3972.848</t>
+          <t>-4088.81005990871</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3212.122</t>
+          <t>-2829.50474050699</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3801.748</t>
+          <t>-3114.65542321134</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>3815.19</t>
+          <t>-1571.60227643267</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>3814.434</t>
+          <t>-3632.47483107035</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>3836.942</t>
+          <t>135.794739915094</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3841.651</t>
+          <t>-3275.53502800182</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>4051.951</t>
+          <t>995.248787586873</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3867.751</t>
+          <t>891.569975455532</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3904.434</t>
+          <t>909.401382956829</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11811.881</t>
+          <t>-1078561218.28781</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6318.734</t>
+          <t>-1703650145.81921</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6420.371</t>
+          <t>-1482540421.1985</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7048.256</t>
+          <t>-1503642771.87724</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7519.001</t>
+          <t>-1379319169.25985</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8073.594</t>
+          <t>-1499029273.82427</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7671.68</t>
+          <t>-1534548817.66825</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7364.462</t>
+          <t>-1436883993.70045</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7363.533</t>
+          <t>-1674642803.20535</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7784.687</t>
+          <t>-1810801211.11597</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7714.459</t>
+          <t>-2298835092.47378</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7934.601</t>
+          <t>-2173296329.88267</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7764.417</t>
+          <t>-1705977765.06641</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>8336.569</t>
+          <t>-2372092491.37703</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6711.282</t>
+          <t>-2066284240.78006</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6721.596</t>
+          <t>-1960494291.78204</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>7121.093</t>
+          <t>-2209691415.1631</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6685.02</t>
+          <t>-2319476807.04499</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>6864.66</t>
+          <t>-2272953449.98297</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6152.461</t>
+          <t>-1721876216.06758</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>5842.436</t>
+          <t>-1526311157.77454</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>5735.033</t>
+          <t>-1844662925.27578</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>5709.487</t>
+          <t>-1178149710.73994</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5910.471</t>
+          <t>-1529967299.54405</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>6133.602</t>
+          <t>-1349459524.8455</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>6137.64</t>
+          <t>-1584940259.68943</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>6148.43</t>
+          <t>-1518487000.60093</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>31736.4987599267</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>34294.645616674</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>37266.605673639</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>39986.355263746</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>42044.4990907946</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>45719.8638938757</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>47808.3676571128</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>48686.0025426521</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>49857.0093001248</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>50666.55107575</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>53279.113127622</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>55037.8679825875</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>58622.0347997291</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>61298.9629784816</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>62527.5212816837</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>61957.2748341288</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>66076.4801637276</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>66263.500626587</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>67844.0125720996</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>72324.4315489808</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>73248.0896204638</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>76656.5231251849</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>80866.5921029686</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>90034.4610126276</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>84659.0793008962</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>88337.4253046784</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>94534.7009435504</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2664.7</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2566.8</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2631.492</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2875.64</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2876.984</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2927.637</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2939.877</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2915.833</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2926.707</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2843.064</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2840.886</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2892.19</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2917.359</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2929.652</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2609.518</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2773.717</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2762.69</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2780.817</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>2758.647</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2661.354</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>2728.507</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2697.129</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2759.088</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>2800.758</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2968.126</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>2825.767</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2850.768</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>46843.5806233725</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>51782.7600832847</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>54618.6660290064</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>57410.639932247</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>58888.7507419737</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>64228.2965664495</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>69771.4853563246</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>71908.2702203902</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>74698.8432885357</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>76364.5337024765</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>80826.0680139168</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>83560.8398509499</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>88794.928831558</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>95940.6565768251</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>95186.5532996791</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>96160.8833735</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>100717.095992916</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>102884.375841087</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>104154.747429103</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>107288.675934895</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>109887.822879017</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>112109.486930217</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>118741.785184818</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>136282.28424214</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>123755.086232096</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>132763.658777584</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>143869.197296508</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3554.589</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2763.73</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2722.286</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2825.868</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2588.904</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2776.175</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2825.548</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2662.783</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2667.485</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2590.681</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2859.866</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2822.422</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2521.736</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>3209.215</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2714.739</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2594.7</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2524.335</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2627.537</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2614.649</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2415.593</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2179.469</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2248.958</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2054.334</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>2942.053</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2387.071</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>2743.467</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2943.33</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>5.05</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-6.43</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-8.46</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>11.78</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>21.42</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>22.76</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>65.85</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>55.88</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>57.38</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>75.05</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>69.61</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>86.77</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>30.58</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>69.75</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>40.98</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>32.65</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>19.526</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7.143</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>6.578</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>7.157</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6.813</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>5.807</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5.835</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>5.678</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4.832</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>5.142</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4.102</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.113</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4.114</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.49</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>3.581</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>3.851</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>221850.427</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>219005.141</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>221114.243</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>228920.566</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>234924.801</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>234421.364</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>236670.477</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>236645.988</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>42236.0820848835</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>39736.428806288</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>43200.8885386521</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>47088.7882980558</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>51639.6953066989</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>54797.786054299</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>57399.3238533692</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>58194.1200265438</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>58446.2504298793</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>63076.7737755868</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>63996.4871953675</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>68834.767270613</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>76056.770982075</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>73122.4982976881</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>64157.3675935038</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>70110.0372988328</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>73477.5417260253</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>73847.6447183328</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>75175.1227524623</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>74436.9971716121</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>75815.2031500511</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>78254.5406231732</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>79243.5086955323</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>65432.8648261487</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>86749.1205989899</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>80117.871480745</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>69375.585560297</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3734219025.22882</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2586159000.00004</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2492023999.99807</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2848492999.99927</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2884092000.00033</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3111361999.99875</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3158355999.99828</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3233125999.99917</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3274489000.00058</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3213936999.99859</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3304032000.00004</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3421877000.00076</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4182387999.99967</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4261446999.99949</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3853172999.9995</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3172753000.00073</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3934828999.99868</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3972848000.00034</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3212122000.00164</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3801748032.30918</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>3815189832.69623</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>3814434278.28516</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3836942275.78514</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>3841651010.92335</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>4051951028.89277</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>3867751166.44312</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>3904433576.57089</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4546835431.66232</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4044120000.00004</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4173151999.99902</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4565121999.99841</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4501087999.99945</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4758343999.9995</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4747795999.99841</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4762789999.99951</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4822461000.00052</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4701228999.9987</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4740226000.00008</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4833121000.0005</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4904023999.99952</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4975563999.99954</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4572333999.99951</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>4645949000.00006</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>4654642999.99877</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>4702879000.00026</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>4685242000.00107</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>4515742174.43629</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>4536367757.16935</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>4532434968.90499</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>4573942537.44066</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>4587027470.24489</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>4849613582.63034</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>4659658596.42348</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4713530011.11967</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2664699981.77044</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2566800108.80876</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2631491925.97292</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2875640497.805</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2876984231.39058</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2927636523.8235</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2939877358.866</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2915832562.68029</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2926707404.72239</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2843063698.20494</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2840886238.58517</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2892190151.34009</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2917359419.68206</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2929651961.61163</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2609517940.70112</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2773716586.50165</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2762690277.713</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2780817162.35018</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2758647390.09279</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2661353968.42456</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2728507488.94878</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2697128591.05493</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2759088200.59761</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>2800757688.45321</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2968126198.34387</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>2825766937.58723</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2850767769.77969</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2378156.83269949</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2090300.00000019</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2116399.99999964</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2197200.00000018</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2269300</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2412699.99999986</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2451000.00000067</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2488799.99999972</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2488299.99999971</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2478299.9999998</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2460699.99999963</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2480500.00000022</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2523300.00000051</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2570600.00000041</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2352800.00000089</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2447200.00000072</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2434999.99999934</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2462500.00000034</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2471300.00000021</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2388283.29821005</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2404311.89423249</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2405847.18827674</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2422113.77913696</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2422558.3201327</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2558133.7498214</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>2446515.00069052</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2473261.50307585</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2009267.29672399</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1771700.00000013</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1774799.99999964</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1867799.99999998</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1952500</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2091900.00000005</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2129600.00000064</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2179099.99999963</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2179699.99999967</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2172499.99999978</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2163299.99999971</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2177500.00000024</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2210600.0000006</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2257700.00000038</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2033600.00000087</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2113500.00000064</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2107699.99999932</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2132700.00000041</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2135100.00000021</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2061533.51421916</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2077109.54492024</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2082778.27859179</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2089971.72500842</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2086139.4178596</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2196386.40922068</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2089789.78842855</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2108881.06716577</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4546835431.66232</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4044120000.00004</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4173151999.99902</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4565121999.99841</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4501087999.99945</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4758343999.9995</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4747795999.99841</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4762789999.99951</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4822461000.00052</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4701228999.9987</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4740226000.00008</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4833121000.0005</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4904023999.99952</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4975563999.99954</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4572333999.99951</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>4645949000.00006</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>4654642999.99877</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4702879000.00026</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4685242000.00107</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>4515742174.43629</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>4536367757.16935</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>4532434968.90499</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>4573942537.44066</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>4587027470.24489</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>4849613582.63034</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>4659658596.42348</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>4713530011.11967</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3734219025.22882</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2586159000.00004</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2492023999.99807</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2848492999.99927</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2884092000.00033</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3111361999.99875</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3158355999.99828</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3233125999.99917</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3274489000.00058</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3213936999.99859</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3304032000.00004</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3421877000.00076</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4182387999.99967</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4261446999.99949</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3853172999.9995</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3172753000.00073</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3934828999.99868</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3972848000.00034</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3212122000.00164</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3801748032.30918</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>3815189832.69623</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>3814434278.28516</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>3836942275.78514</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>3841651010.92335</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>4051951028.89277</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>3867751166.44312</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>3904433576.57089</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>175721.949624342</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>176544.821713752</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>189500.043268624</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>201525.100363404</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>212852.320813665</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>245390.499488876</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>252757.526235691</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>257795.353220195</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>263294.071644775</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>278559.822149439</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>298356.208855611</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>318184.936632884</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>345299.441973469</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>359199.061783256</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>322977.511116371</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>340034.42149458</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>360743.953168495</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>367240.543381338</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>368104.275973607</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>375320.550498785</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>383632.056078521</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>394325.101803166</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>413657.093340666</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>429165.069070396</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>442990.262661281</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>453304.971990409</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>453367.621417586</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>52650.917434092</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>56539.2377763761</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>60326.5586879035</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>63465.3464183315</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>65673.9425376231</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>71054.7300975611</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>76239.6198597981</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78462.0598962817</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>81553.4331246336</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>83439.3579139732</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>88203.3762400658</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>90852.3159429836</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>96660.5038075269</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>105710.812287551</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>103164.853091084</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>103647.86548049</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>109336.660534451</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>112021.698725256</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>113679.814729037</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>116600.870908694</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>119516.341432885</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>122672.23093261</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>129586.837309993</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>150537.526651832</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>135596.050961941</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>145492.146234474</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>159551.790372201</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
